--- a/artfynd/A 19224-2026 artfynd.xlsx
+++ b/artfynd/A 19224-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133822960</v>
       </c>
       <c r="B2" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133822676</v>
       </c>
       <c r="B3" t="n">
-        <v>79391</v>
+        <v>79398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>133822917</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>133822959</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>133822716</v>
       </c>
       <c r="B6" t="n">
-        <v>78717</v>
+        <v>78724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>133822824</v>
       </c>
       <c r="B7" t="n">
-        <v>79383</v>
+        <v>79390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>133822660</v>
       </c>
       <c r="B8" t="n">
-        <v>79391</v>
+        <v>79398</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>133822659</v>
       </c>
       <c r="B9" t="n">
-        <v>79391</v>
+        <v>79398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 19224-2026 artfynd.xlsx
+++ b/artfynd/A 19224-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133822960</v>
+        <v>133822659</v>
       </c>
       <c r="B2" t="n">
-        <v>79366</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379073</v>
+        <v>379097</v>
       </c>
       <c r="R2" t="n">
-        <v>6685454</v>
+        <v>6685473</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>06:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>06:46</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på tall</t>
+          <t>på gran ca 20cm i diam I bh</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133822676</v>
+        <v>133822660</v>
       </c>
       <c r="B3" t="n">
-        <v>79398</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379104</v>
+        <v>379074</v>
       </c>
       <c r="R3" t="n">
-        <v>6685461</v>
+        <v>6685438</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på tallstam rullstol med blåslav</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133822917</v>
+        <v>133822676</v>
       </c>
       <c r="B4" t="n">
-        <v>79366</v>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379071</v>
+        <v>379104</v>
       </c>
       <c r="R4" t="n">
-        <v>6685437</v>
+        <v>6685461</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>på gran I slänt</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133822959</v>
+        <v>133822678</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>79405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379079</v>
+        <v>379081</v>
       </c>
       <c r="R5" t="n">
-        <v>6685441</v>
+        <v>6685307</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på gran I slänt</t>
+          <t>på granar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133822716</v>
+        <v>133822917</v>
       </c>
       <c r="B6" t="n">
-        <v>78724</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6443</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379074</v>
+        <v>379071</v>
       </c>
       <c r="R6" t="n">
-        <v>6685441</v>
+        <v>6685437</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>osäker artbestämning</t>
+          <t>på gran I slänt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,32 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133822824</v>
+        <v>133822959</v>
       </c>
       <c r="B7" t="n">
-        <v>79390</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>379076</v>
+        <v>379079</v>
       </c>
       <c r="R7" t="n">
-        <v>6685451</v>
+        <v>6685441</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>på smal tall på höjd</t>
+          <t>på gran I slänt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,32 +1342,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133822660</v>
+        <v>133822960</v>
       </c>
       <c r="B8" t="n">
-        <v>79398</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>379074</v>
+        <v>379073</v>
       </c>
       <c r="R8" t="n">
-        <v>6685438</v>
+        <v>6685454</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>på tallstam rullstol med blåslav</t>
+          <t>på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,32 +1454,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133822659</v>
+        <v>133822824</v>
       </c>
       <c r="B9" t="n">
-        <v>79398</v>
+        <v>79397</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>379097</v>
+        <v>379076</v>
       </c>
       <c r="R9" t="n">
-        <v>6685473</v>
+        <v>6685451</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06:46</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>06:46</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>på gran ca 20cm i diam I bh</t>
+          <t>på smal tall på höjd</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,6 +1563,492 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133822716</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78731</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bastvålen, Östmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>379074</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6685441</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>osäker artbestämning</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131088919</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bastvålen, Östmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>379111</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6685490</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131088920</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bastvålen, Östmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>379023</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6685330</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133822890</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56896</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bastvålen, Östmark, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>379070</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6685304</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Östmark</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>vilade under platta, kröp ner i håla/bo under marken</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Eduardo Ottimofiore, Annelie Thor</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19224-2026 artfynd.xlsx
+++ b/artfynd/A 19224-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822659</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822660</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822676</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822678</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822917</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822959</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822960</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822824</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822716</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1806,6 +1856,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088919</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1937,6 +1992,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131088920</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2049,8 +2109,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133822890</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>